--- a/dashboard/public/subject_upload_demo.xlsx
+++ b/dashboard/public/subject_upload_demo.xlsx
@@ -8,14 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mutiur\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66FF902-D901-45E2-A9B9-F6BC7465790E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B60223-75BD-46D7-91B5-52D86D23DF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Subjects" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -592,6 +603,7 @@
         <v>33</v>
       </c>
       <c r="E2">
+        <f ca="1">YEAR(TODAY())</f>
         <v>2026</v>
       </c>
       <c r="F2" t="s">
@@ -618,6 +630,7 @@
         <v>17</v>
       </c>
       <c r="E3">
+        <f t="shared" ref="E3:E65" ca="1" si="0">YEAR(TODAY())</f>
         <v>2026</v>
       </c>
       <c r="F3" t="s">
@@ -644,6 +657,7 @@
         <v>33</v>
       </c>
       <c r="E4">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="F4" t="s">
@@ -670,6 +684,7 @@
         <v>17</v>
       </c>
       <c r="E5">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="F5" t="s">
@@ -696,6 +711,7 @@
         <v>33</v>
       </c>
       <c r="E6">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G6" t="s">
@@ -719,6 +735,7 @@
         <v>33</v>
       </c>
       <c r="E7">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G7" t="s">
@@ -742,6 +759,7 @@
         <v>33</v>
       </c>
       <c r="E8">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G8" t="s">
@@ -765,6 +783,7 @@
         <v>33</v>
       </c>
       <c r="E9">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G9" t="s">
@@ -788,6 +807,7 @@
         <v>17</v>
       </c>
       <c r="E10">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G10" t="s">
@@ -808,6 +828,7 @@
         <v>50</v>
       </c>
       <c r="E11">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G11" t="s">
@@ -831,6 +852,7 @@
         <v>33</v>
       </c>
       <c r="E12">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="F12" t="s">
@@ -857,6 +879,7 @@
         <v>17</v>
       </c>
       <c r="E13">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="F13" t="s">
@@ -883,6 +906,7 @@
         <v>33</v>
       </c>
       <c r="E14">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="F14" t="s">
@@ -909,6 +933,7 @@
         <v>17</v>
       </c>
       <c r="E15">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="F15" t="s">
@@ -935,6 +960,7 @@
         <v>33</v>
       </c>
       <c r="E16">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G16" t="s">
@@ -958,6 +984,7 @@
         <v>33</v>
       </c>
       <c r="E17">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G17" t="s">
@@ -981,6 +1008,7 @@
         <v>33</v>
       </c>
       <c r="E18">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G18" t="s">
@@ -1004,6 +1032,7 @@
         <v>33</v>
       </c>
       <c r="E19">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G19" t="s">
@@ -1027,6 +1056,7 @@
         <v>17</v>
       </c>
       <c r="E20">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G20" t="s">
@@ -1047,6 +1077,7 @@
         <v>50</v>
       </c>
       <c r="E21">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G21" t="s">
@@ -1070,6 +1101,7 @@
         <v>33</v>
       </c>
       <c r="E22">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="F22" t="s">
@@ -1096,6 +1128,7 @@
         <v>17</v>
       </c>
       <c r="E23">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="F23" t="s">
@@ -1122,6 +1155,7 @@
         <v>33</v>
       </c>
       <c r="E24">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="F24" t="s">
@@ -1148,6 +1182,7 @@
         <v>17</v>
       </c>
       <c r="E25">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="F25" t="s">
@@ -1174,6 +1209,7 @@
         <v>33</v>
       </c>
       <c r="E26">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G26" t="s">
@@ -1197,6 +1233,7 @@
         <v>33</v>
       </c>
       <c r="E27">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G27" t="s">
@@ -1220,6 +1257,7 @@
         <v>33</v>
       </c>
       <c r="E28">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G28" t="s">
@@ -1243,6 +1281,7 @@
         <v>33</v>
       </c>
       <c r="E29">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G29" t="s">
@@ -1266,6 +1305,7 @@
         <v>17</v>
       </c>
       <c r="E30">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G30" t="s">
@@ -1286,6 +1326,7 @@
         <v>50</v>
       </c>
       <c r="E31">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G31" t="s">
@@ -1309,6 +1350,7 @@
         <v>33</v>
       </c>
       <c r="E32">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="F32" t="s">
@@ -1347,6 +1389,7 @@
         <v>33</v>
       </c>
       <c r="E33">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="F33" t="s">
@@ -1385,6 +1428,7 @@
         <v>33</v>
       </c>
       <c r="E34">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="F34" t="s">
@@ -1423,6 +1467,7 @@
         <v>33</v>
       </c>
       <c r="E35">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="F35" t="s">
@@ -1461,6 +1506,7 @@
         <v>33</v>
       </c>
       <c r="E36">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G36" t="s">
@@ -1496,6 +1542,7 @@
         <v>33</v>
       </c>
       <c r="E37">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G37" t="s">
@@ -1531,6 +1578,7 @@
         <v>33</v>
       </c>
       <c r="E38">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G38" t="s">
@@ -1569,6 +1617,7 @@
         <v>33</v>
       </c>
       <c r="E39">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G39" t="s">
@@ -1607,6 +1656,7 @@
         <v>33</v>
       </c>
       <c r="E40">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G40" t="s">
@@ -1651,6 +1701,7 @@
         <v>33</v>
       </c>
       <c r="E41">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G41" t="s">
@@ -1689,6 +1740,7 @@
         <v>33</v>
       </c>
       <c r="E42">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G42" t="s">
@@ -1733,6 +1785,7 @@
         <v>33</v>
       </c>
       <c r="E43">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G43" t="s">
@@ -1771,6 +1824,7 @@
         <v>33</v>
       </c>
       <c r="E44">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G44" t="s">
@@ -1815,6 +1869,7 @@
         <v>33</v>
       </c>
       <c r="E45">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G45" t="s">
@@ -1853,6 +1908,7 @@
         <v>8</v>
       </c>
       <c r="E46">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G46" t="s">
@@ -1882,6 +1938,7 @@
         <v>33</v>
       </c>
       <c r="E47">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G47" t="s">
@@ -1926,6 +1983,7 @@
         <v>33</v>
       </c>
       <c r="E48">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G48" t="s">
@@ -1970,6 +2028,7 @@
         <v>33</v>
       </c>
       <c r="E49">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="F49" t="s">
@@ -2008,6 +2067,7 @@
         <v>33</v>
       </c>
       <c r="E50">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="F50" t="s">
@@ -2046,6 +2106,7 @@
         <v>33</v>
       </c>
       <c r="E51">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="F51" t="s">
@@ -2084,6 +2145,7 @@
         <v>33</v>
       </c>
       <c r="E52">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="F52" t="s">
@@ -2122,6 +2184,7 @@
         <v>33</v>
       </c>
       <c r="E53">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G53" t="s">
@@ -2157,6 +2220,7 @@
         <v>33</v>
       </c>
       <c r="E54">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G54" t="s">
@@ -2192,6 +2256,7 @@
         <v>33</v>
       </c>
       <c r="E55">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G55" t="s">
@@ -2230,6 +2295,7 @@
         <v>33</v>
       </c>
       <c r="E56">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G56" t="s">
@@ -2268,6 +2334,7 @@
         <v>33</v>
       </c>
       <c r="E57">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G57" t="s">
@@ -2312,6 +2379,7 @@
         <v>33</v>
       </c>
       <c r="E58">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G58" t="s">
@@ -2350,6 +2418,7 @@
         <v>33</v>
       </c>
       <c r="E59">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G59" t="s">
@@ -2394,6 +2463,7 @@
         <v>33</v>
       </c>
       <c r="E60">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G60" t="s">
@@ -2432,6 +2502,7 @@
         <v>33</v>
       </c>
       <c r="E61">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G61" t="s">
@@ -2476,6 +2547,7 @@
         <v>33</v>
       </c>
       <c r="E62">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G62" t="s">
@@ -2514,6 +2586,7 @@
         <v>8</v>
       </c>
       <c r="E63">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G63" t="s">
@@ -2543,6 +2616,7 @@
         <v>33</v>
       </c>
       <c r="E64">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G64" t="s">
@@ -2587,6 +2661,7 @@
         <v>33</v>
       </c>
       <c r="E65">
+        <f t="shared" ca="1" si="0"/>
         <v>2026</v>
       </c>
       <c r="G65" t="s">
@@ -2620,7 +2695,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:D1 A2 C2:D2 E2:F2 G3 H1 E4 G1 E1:F1 E3:F3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:D1 A2 C2:D2 F2 G3 H1 G1 E1:F1 F3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard/public/subject_upload_demo.xlsx
+++ b/dashboard/public/subject_upload_demo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mutiur\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\School\dashboard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B60223-75BD-46D7-91B5-52D86D23DF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2B2D4B-2427-40BA-AACA-ED1355F096C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Subjects" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="40">
   <si>
     <t>name</t>
   </si>
@@ -148,16 +148,25 @@
   </si>
   <si>
     <t>Humanities</t>
+  </si>
+  <si>
+    <t>marking_scheme</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -183,8 +192,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -524,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:P65"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
@@ -542,7 +554,7 @@
     <col min="17" max="17" width="18.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -588,8 +600,11 @@
       <c r="O1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -616,7 +631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -643,7 +658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -670,7 +685,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -697,7 +712,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -721,7 +736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -745,7 +760,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -769,7 +784,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -793,7 +808,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -817,7 +832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -838,7 +853,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -865,7 +880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -892,7 +907,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -919,7 +934,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -946,7 +961,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>

--- a/dashboard/public/subject_upload_demo.xlsx
+++ b/dashboard/public/subject_upload_demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\School\dashboard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2B2D4B-2427-40BA-AACA-ED1355F096C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0214235F-A4F1-4E10-AD63-B24814F6D15F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Subjects" sheetId="1" r:id="rId1"/>
@@ -63,9 +63,6 @@
     <t>practical_pass_mark</t>
   </si>
   <si>
-    <t>department</t>
-  </si>
-  <si>
     <t>year</t>
   </si>
   <si>
@@ -151,6 +148,9 @@
   </si>
   <si>
     <t>marking_scheme</t>
+  </si>
+  <si>
+    <t>group</t>
   </si>
 </sst>
 </file>
@@ -568,19 +568,19 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" t="s">
-        <v>10</v>
+      <c r="I1" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="J1" t="s">
         <v>4</v>
@@ -601,12 +601,12 @@
         <v>9</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>6</v>
@@ -622,10 +622,10 @@
         <v>2026</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -633,7 +633,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -649,10 +649,10 @@
         <v>2026</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -660,7 +660,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -676,10 +676,10 @@
         <v>2026</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -687,7 +687,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>6</v>
@@ -703,10 +703,10 @@
         <v>2026</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -714,7 +714,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6">
         <v>6</v>
@@ -730,7 +730,7 @@
         <v>2026</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -738,7 +738,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -754,7 +754,7 @@
         <v>2026</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8">
         <v>6</v>
@@ -778,7 +778,7 @@
         <v>2026</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H8">
         <v>7</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9">
         <v>6</v>
@@ -802,7 +802,7 @@
         <v>2026</v>
       </c>
       <c r="G9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H9">
         <v>8</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10">
         <v>6</v>
@@ -826,7 +826,7 @@
         <v>2026</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H10">
         <v>9</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>6</v>
@@ -847,7 +847,7 @@
         <v>2026</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H11">
         <v>10</v>
@@ -855,7 +855,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>7</v>
@@ -871,10 +871,10 @@
         <v>2026</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>7</v>
@@ -898,10 +898,10 @@
         <v>2026</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>7</v>
@@ -925,10 +925,10 @@
         <v>2026</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H14">
         <v>3</v>
@@ -936,7 +936,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15">
         <v>7</v>
@@ -952,10 +952,10 @@
         <v>2026</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H15">
         <v>4</v>
@@ -963,7 +963,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <v>7</v>
@@ -979,7 +979,7 @@
         <v>2026</v>
       </c>
       <c r="G16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H16">
         <v>5</v>
@@ -987,7 +987,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>7</v>
@@ -1003,7 +1003,7 @@
         <v>2026</v>
       </c>
       <c r="G17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H17">
         <v>6</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18">
         <v>7</v>
@@ -1027,7 +1027,7 @@
         <v>2026</v>
       </c>
       <c r="G18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H18">
         <v>7</v>
@@ -1035,7 +1035,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19">
         <v>7</v>
@@ -1051,7 +1051,7 @@
         <v>2026</v>
       </c>
       <c r="G19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H19">
         <v>8</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>7</v>
@@ -1075,7 +1075,7 @@
         <v>2026</v>
       </c>
       <c r="G20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H20">
         <v>9</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21">
         <v>7</v>
@@ -1096,7 +1096,7 @@
         <v>2026</v>
       </c>
       <c r="G21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H21">
         <v>10</v>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B22">
         <v>8</v>
@@ -1120,10 +1120,10 @@
         <v>2026</v>
       </c>
       <c r="F22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1131,7 +1131,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23">
         <v>8</v>
@@ -1147,10 +1147,10 @@
         <v>2026</v>
       </c>
       <c r="F23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H23">
         <v>2</v>
@@ -1158,26 +1158,26 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24">
+        <v>100</v>
+      </c>
+      <c r="D24">
+        <v>33</v>
+      </c>
+      <c r="E24">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="F24" t="s">
         <v>22</v>
       </c>
-      <c r="B24">
-        <v>8</v>
-      </c>
-      <c r="C24">
-        <v>100</v>
-      </c>
-      <c r="D24">
-        <v>33</v>
-      </c>
-      <c r="E24">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026</v>
-      </c>
-      <c r="F24" t="s">
-        <v>23</v>
-      </c>
       <c r="G24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H24">
         <v>3</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25">
         <v>8</v>
@@ -1201,10 +1201,10 @@
         <v>2026</v>
       </c>
       <c r="F25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H25">
         <v>4</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26">
         <v>8</v>
@@ -1228,7 +1228,7 @@
         <v>2026</v>
       </c>
       <c r="G26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H26">
         <v>5</v>
@@ -1236,7 +1236,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27">
         <v>8</v>
@@ -1252,7 +1252,7 @@
         <v>2026</v>
       </c>
       <c r="G27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H27">
         <v>6</v>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B28">
         <v>8</v>
@@ -1276,7 +1276,7 @@
         <v>2026</v>
       </c>
       <c r="G28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H28">
         <v>7</v>
@@ -1284,7 +1284,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29">
         <v>8</v>
@@ -1300,7 +1300,7 @@
         <v>2026</v>
       </c>
       <c r="G29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H29">
         <v>8</v>
@@ -1308,7 +1308,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30">
         <v>8</v>
@@ -1324,7 +1324,7 @@
         <v>2026</v>
       </c>
       <c r="G30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H30">
         <v>9</v>
@@ -1332,7 +1332,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31">
         <v>8</v>
@@ -1345,7 +1345,7 @@
         <v>2026</v>
       </c>
       <c r="G31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H31">
         <v>10</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B32">
         <v>9</v>
@@ -1369,10 +1369,10 @@
         <v>2026</v>
       </c>
       <c r="F32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -1392,7 +1392,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B33">
         <v>9</v>
@@ -1408,10 +1408,10 @@
         <v>2026</v>
       </c>
       <c r="F33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H33">
         <v>2</v>
@@ -1431,7 +1431,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B34">
         <v>9</v>
@@ -1447,10 +1447,10 @@
         <v>2026</v>
       </c>
       <c r="F34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H34">
         <v>3</v>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B35">
         <v>9</v>
@@ -1486,10 +1486,10 @@
         <v>2026</v>
       </c>
       <c r="F35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H35">
         <v>4</v>
@@ -1509,7 +1509,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B36">
         <v>9</v>
@@ -1525,7 +1525,7 @@
         <v>2026</v>
       </c>
       <c r="G36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H36">
         <v>5</v>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B37">
         <v>9</v>
@@ -1561,7 +1561,7 @@
         <v>2026</v>
       </c>
       <c r="G37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H37">
         <v>6</v>
@@ -1581,7 +1581,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B38">
         <v>9</v>
@@ -1597,13 +1597,13 @@
         <v>2026</v>
       </c>
       <c r="G38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H38">
         <v>7</v>
       </c>
       <c r="I38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J38">
         <v>70</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B39">
         <v>9</v>
@@ -1636,13 +1636,13 @@
         <v>2026</v>
       </c>
       <c r="G39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H39">
         <v>7</v>
       </c>
       <c r="I39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J39">
         <v>70</v>
@@ -1659,7 +1659,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B40">
         <v>9</v>
@@ -1675,13 +1675,13 @@
         <v>2026</v>
       </c>
       <c r="G40" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H40">
         <v>8</v>
       </c>
       <c r="I40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J40">
         <v>50</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B41">
         <v>9</v>
@@ -1720,13 +1720,13 @@
         <v>2026</v>
       </c>
       <c r="G41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H41">
         <v>8</v>
       </c>
       <c r="I41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J41">
         <v>70</v>
@@ -1743,7 +1743,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B42">
         <v>9</v>
@@ -1759,13 +1759,13 @@
         <v>2026</v>
       </c>
       <c r="G42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H42">
         <v>9</v>
       </c>
       <c r="I42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J42">
         <v>50</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B43">
         <v>9</v>
@@ -1804,13 +1804,13 @@
         <v>2026</v>
       </c>
       <c r="G43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H43">
         <v>9</v>
       </c>
       <c r="I43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J43">
         <v>70</v>
@@ -1827,7 +1827,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B44">
         <v>9</v>
@@ -1843,13 +1843,13 @@
         <v>2026</v>
       </c>
       <c r="G44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H44">
         <v>10</v>
       </c>
       <c r="I44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J44">
         <v>50</v>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B45">
         <v>9</v>
@@ -1888,13 +1888,13 @@
         <v>2026</v>
       </c>
       <c r="G45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H45">
         <v>10</v>
       </c>
       <c r="I45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J45">
         <v>70</v>
@@ -1911,7 +1911,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B46">
         <v>9</v>
@@ -1927,7 +1927,7 @@
         <v>2026</v>
       </c>
       <c r="G46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H46">
         <v>11</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B47">
         <v>9</v>
@@ -1957,13 +1957,13 @@
         <v>2026</v>
       </c>
       <c r="G47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H47">
         <v>12</v>
       </c>
       <c r="I47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J47">
         <v>50</v>
@@ -1986,7 +1986,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B48">
         <v>9</v>
@@ -2002,13 +2002,13 @@
         <v>2026</v>
       </c>
       <c r="G48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H48">
         <v>12</v>
       </c>
       <c r="I48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J48">
         <v>50</v>
@@ -2031,7 +2031,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B49">
         <v>10</v>
@@ -2047,10 +2047,10 @@
         <v>2026</v>
       </c>
       <c r="F49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B50">
         <v>10</v>
@@ -2086,10 +2086,10 @@
         <v>2026</v>
       </c>
       <c r="F50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H50">
         <v>2</v>
@@ -2109,26 +2109,26 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>21</v>
+      </c>
+      <c r="B51">
+        <v>10</v>
+      </c>
+      <c r="C51">
+        <v>100</v>
+      </c>
+      <c r="D51">
+        <v>33</v>
+      </c>
+      <c r="E51">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="F51" t="s">
         <v>22</v>
       </c>
-      <c r="B51">
-        <v>10</v>
-      </c>
-      <c r="C51">
-        <v>100</v>
-      </c>
-      <c r="D51">
-        <v>33</v>
-      </c>
-      <c r="E51">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026</v>
-      </c>
-      <c r="F51" t="s">
-        <v>23</v>
-      </c>
       <c r="G51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H51">
         <v>3</v>
@@ -2148,7 +2148,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B52">
         <v>10</v>
@@ -2164,10 +2164,10 @@
         <v>2026</v>
       </c>
       <c r="F52" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H52">
         <v>4</v>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B53">
         <v>10</v>
@@ -2203,7 +2203,7 @@
         <v>2026</v>
       </c>
       <c r="G53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H53">
         <v>5</v>
@@ -2223,7 +2223,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B54">
         <v>10</v>
@@ -2239,7 +2239,7 @@
         <v>2026</v>
       </c>
       <c r="G54" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H54">
         <v>6</v>
@@ -2259,7 +2259,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B55">
         <v>10</v>
@@ -2275,13 +2275,13 @@
         <v>2026</v>
       </c>
       <c r="G55" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H55">
         <v>7</v>
       </c>
       <c r="I55" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J55">
         <v>70</v>
@@ -2298,7 +2298,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B56">
         <v>10</v>
@@ -2314,13 +2314,13 @@
         <v>2026</v>
       </c>
       <c r="G56" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H56">
         <v>7</v>
       </c>
       <c r="I56" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J56">
         <v>70</v>
@@ -2337,7 +2337,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B57">
         <v>10</v>
@@ -2353,13 +2353,13 @@
         <v>2026</v>
       </c>
       <c r="G57" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H57">
         <v>8</v>
       </c>
       <c r="I57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J57">
         <v>50</v>
@@ -2382,7 +2382,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B58">
         <v>10</v>
@@ -2398,13 +2398,13 @@
         <v>2026</v>
       </c>
       <c r="G58" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H58">
         <v>8</v>
       </c>
       <c r="I58" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J58">
         <v>70</v>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B59">
         <v>10</v>
@@ -2437,13 +2437,13 @@
         <v>2026</v>
       </c>
       <c r="G59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H59">
         <v>9</v>
       </c>
       <c r="I59" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J59">
         <v>50</v>
@@ -2466,7 +2466,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B60">
         <v>10</v>
@@ -2482,13 +2482,13 @@
         <v>2026</v>
       </c>
       <c r="G60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H60">
         <v>9</v>
       </c>
       <c r="I60" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J60">
         <v>70</v>
@@ -2505,7 +2505,7 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B61">
         <v>10</v>
@@ -2521,13 +2521,13 @@
         <v>2026</v>
       </c>
       <c r="G61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H61">
         <v>10</v>
       </c>
       <c r="I61" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J61">
         <v>50</v>
@@ -2550,29 +2550,29 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62">
+        <v>10</v>
+      </c>
+      <c r="C62">
+        <v>100</v>
+      </c>
+      <c r="D62">
+        <v>33</v>
+      </c>
+      <c r="E62">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="G62" t="s">
+        <v>17</v>
+      </c>
+      <c r="H62">
+        <v>10</v>
+      </c>
+      <c r="I62" t="s">
         <v>37</v>
-      </c>
-      <c r="B62">
-        <v>10</v>
-      </c>
-      <c r="C62">
-        <v>100</v>
-      </c>
-      <c r="D62">
-        <v>33</v>
-      </c>
-      <c r="E62">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026</v>
-      </c>
-      <c r="G62" t="s">
-        <v>18</v>
-      </c>
-      <c r="H62">
-        <v>10</v>
-      </c>
-      <c r="I62" t="s">
-        <v>38</v>
       </c>
       <c r="J62">
         <v>70</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B63">
         <v>10</v>
@@ -2605,7 +2605,7 @@
         <v>2026</v>
       </c>
       <c r="G63" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H63">
         <v>11</v>
@@ -2619,7 +2619,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B64">
         <v>10</v>
@@ -2635,13 +2635,13 @@
         <v>2026</v>
       </c>
       <c r="G64" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H64">
         <v>12</v>
       </c>
       <c r="I64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J64">
         <v>50</v>
@@ -2664,7 +2664,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B65">
         <v>10</v>
@@ -2680,13 +2680,13 @@
         <v>2026</v>
       </c>
       <c r="G65" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H65">
         <v>12</v>
       </c>
       <c r="I65" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J65">
         <v>50</v>
@@ -2709,6 +2709,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="A1:D1 A2 C2:D2 F2 G3 H1 G1 E1:F1 F3" numberStoredAsText="1"/>
   </ignoredErrors>
